--- a/testbuild/StructureDefinition-pmd-Bundle-Response.xlsx
+++ b/testbuild/StructureDefinition-pmd-Bundle-Response.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>A response bundle for observations prcessed by Pasientens måledata</t>
+    <t>A response bundle for observations processed by Pasientens måledata</t>
   </si>
   <si>
     <t>Status</t>
@@ -395,16 +395,13 @@
     <t>Bundle.type</t>
   </si>
   <si>
-    <t>document | message | transaction | transaction-response | batch | batch-response | history | searchset | collection</t>
+    <t>batch-response</t>
   </si>
   <si>
     <t>Indicates the purpose of this bundle - how it is intended to be used.</t>
   </si>
   <si>
     <t>It's possible to use a bundle for other purposes (e.g. a document can be accepted as a transaction). This is primarily defined so that there can be specific rules for some of the bundle types.</t>
-  </si>
-  <si>
-    <t>batch-response</t>
   </si>
   <si>
     <t>required</t>
@@ -787,7 +784,7 @@
     <t>Bundle.entry.response.extension</t>
   </si>
   <si>
-    <t>Extension</t>
+    <t>fullUrl identifying the resoruce entry from the original Bundle of Observations</t>
   </si>
   <si>
     <t>An Extension</t>
@@ -808,6 +805,9 @@
   <si>
     <t xml:space="preserve">Extension {http://hl7.no/fhir/vkpobservation/StructureDefinition/PmdBundleResponseEntryIdExtension}
 </t>
+  </si>
+  <si>
+    <t>Extension</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -2086,28 +2086,28 @@
         <v>78</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="T8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X8" t="s" s="2">
+      <c r="Y8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="Y8" t="s" s="2">
+      <c r="Z8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>130</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>78</v>
@@ -2149,15 +2149,15 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2180,16 +2180,16 @@
         <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2239,7 +2239,7 @@
         <v>78</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2260,18 +2260,18 @@
         <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2294,16 +2294,16 @@
         <v>89</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2353,7 +2353,7 @@
         <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -2362,7 +2362,7 @@
         <v>88</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>100</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2408,16 +2408,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2467,7 +2467,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2496,10 +2496,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2522,13 +2522,13 @@
         <v>78</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2579,25 +2579,25 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>78</v>
@@ -2608,14 +2608,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2634,16 +2634,16 @@
         <v>78</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2693,7 +2693,7 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -2705,13 +2705,13 @@
         <v>78</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>78</v>
@@ -2722,14 +2722,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2748,19 +2748,19 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>78</v>
@@ -2809,7 +2809,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -2821,7 +2821,7 @@
         <v>78</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -2838,10 +2838,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2864,13 +2864,13 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2921,7 +2921,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2979,10 +2979,10 @@
         <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3033,7 +3033,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>88</v>
@@ -3062,10 +3062,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3088,13 +3088,13 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3145,7 +3145,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3157,7 +3157,7 @@
         <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -3174,10 +3174,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3200,13 +3200,13 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3257,25 +3257,25 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -3286,14 +3286,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3312,16 +3312,16 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3371,7 +3371,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3383,13 +3383,13 @@
         <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>78</v>
@@ -3400,14 +3400,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3426,19 +3426,19 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -3487,7 +3487,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3499,7 +3499,7 @@
         <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3545,10 +3545,10 @@
         <v>81</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3599,7 +3599,7 @@
         <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3657,13 +3657,13 @@
         <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3713,7 +3713,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3768,13 +3768,13 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3825,7 +3825,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3880,13 +3880,13 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3937,7 +3937,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3946,7 +3946,7 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>100</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3992,13 +3992,13 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4049,25 +4049,25 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -4078,14 +4078,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4104,16 +4104,16 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4163,7 +4163,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4175,13 +4175,13 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -4192,14 +4192,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4218,19 +4218,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -4279,7 +4279,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4291,7 +4291,7 @@
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -4308,10 +4308,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4337,13 +4337,13 @@
         <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4369,14 +4369,14 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>206</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4422,10 +4422,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4448,16 +4448,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4507,7 +4507,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4536,10 +4536,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4562,13 +4562,13 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4619,7 +4619,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -4628,7 +4628,7 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>100</v>
@@ -4648,10 +4648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4674,13 +4674,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4731,25 +4731,25 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -4760,14 +4760,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4786,16 +4786,16 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4845,7 +4845,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4857,13 +4857,13 @@
         <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -4874,14 +4874,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4900,19 +4900,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -4961,7 +4961,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -4973,7 +4973,7 @@
         <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -4990,10 +4990,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5019,10 +5019,10 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5049,14 +5049,14 @@
         <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>223</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>88</v>
@@ -5102,10 +5102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5131,13 +5131,13 @@
         <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5187,7 +5187,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>88</v>
@@ -5216,10 +5216,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5242,13 +5242,13 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5299,7 +5299,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5328,10 +5328,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5354,13 +5354,13 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5411,7 +5411,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5440,10 +5440,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5466,13 +5466,13 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5523,7 +5523,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5578,13 +5578,13 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5635,7 +5635,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5664,10 +5664,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5690,13 +5690,13 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5747,7 +5747,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -5756,7 +5756,7 @@
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
@@ -5776,10 +5776,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5802,13 +5802,13 @@
         <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5859,25 +5859,25 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -5888,10 +5888,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5914,13 +5914,13 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5959,17 +5959,17 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -5981,7 +5981,7 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>78</v>
@@ -6026,13 +6026,13 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6083,7 +6083,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6095,7 +6095,7 @@
         <v>252</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6138,19 +6138,19 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -6199,7 +6199,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6211,7 +6211,7 @@
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
@@ -6254,7 +6254,7 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>255</v>
@@ -6478,7 +6478,7 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>261</v>
@@ -6592,7 +6592,7 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>265</v>
@@ -6706,7 +6706,7 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>269</v>

--- a/testbuild/StructureDefinition-pmd-Bundle-Response.xlsx
+++ b/testbuild/StructureDefinition-pmd-Bundle-Response.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/testbuild/StructureDefinition-pmd-Bundle-Response.xlsx
+++ b/testbuild/StructureDefinition-pmd-Bundle-Response.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.5.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/testbuild/StructureDefinition-pmd-Bundle-Response.xlsx
+++ b/testbuild/StructureDefinition-pmd-Bundle-Response.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="269">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.1</t>
+    <t>0.5.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -601,7 +601,7 @@
     <t>Bundle.entry.fullUrl</t>
   </si>
   <si>
-    <t>URI for resource (Absolute URL server address or URI for UUID/OID)</t>
+    <t>Uniqe id is mandatory and references the original entry in the batch request</t>
   </si>
   <si>
     <t>The Absolute URL for the resource.  The fullUrl SHALL NOT disagree with the id in the resource - i.e. if the fullUrl is not a urn:uuid, the URL shall be version-independent URL consistent with the Resource.id. The fullUrl is a version independent reference to the resource. The fullUrl element SHALL have a value except that: 
@@ -782,36 +782,6 @@
   </si>
   <si>
     <t>Bundle.entry.response.extension</t>
-  </si>
-  <si>
-    <t>fullUrl identifying the resoruce entry from the original Bundle of Observations</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Bundle.entry.response.extension:entryId</t>
-  </si>
-  <si>
-    <t>entryId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.no/fhir/vkpobservation/StructureDefinition/PmdBundleResponseEntryIdExtension}
-</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>Bundle.entry.response.modifierExtension</t>
@@ -1192,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.44140625" customWidth="true" bestFit="true"/>
@@ -1205,7 +1175,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="82.5859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3639,7 +3609,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -5895,11 +5865,11 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>80</v>
@@ -5917,12 +5887,14 @@
         <v>157</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>244</v>
+        <v>158</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -5959,14 +5931,16 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>161</v>
@@ -5987,7 +5961,7 @@
         <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -5998,44 +5972,46 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>250</v>
+        <v>157</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>251</v>
+        <v>165</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6083,7 +6059,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6092,7 +6068,7 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>252</v>
+        <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>162</v>
@@ -6101,7 +6077,7 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -6112,46 +6088,42 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>165</v>
+        <v>246</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6199,25 +6171,25 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>168</v>
+        <v>245</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>162</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -6228,10 +6200,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6239,7 +6211,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>88</v>
@@ -6254,13 +6226,13 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>150</v>
+        <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6311,10 +6283,10 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>88</v>
@@ -6340,10 +6312,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6366,15 +6338,17 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -6423,7 +6397,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6452,10 +6426,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6478,16 +6452,16 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6537,7 +6511,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6566,10 +6540,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6592,16 +6566,16 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6651,7 +6625,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -6663,7 +6637,7 @@
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
@@ -6680,10 +6654,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6706,18 +6680,20 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>190</v>
+        <v>264</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -6765,7 +6741,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -6777,7 +6753,7 @@
         <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
@@ -6789,122 +6765,6 @@
         <v>78</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="P50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN50" t="s" s="2">
         <v>78</v>
       </c>
     </row>
